--- a/data/trans_orig/IP39B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP39B-Provincia-trans_orig.xlsx
@@ -850,7 +850,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3791</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -998,7 +998,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>4105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>5501</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6562</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14566</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3580</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11455</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12114</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23713</t>
+          <t>23518</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18648</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26483</t>
+          <t>26827</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22916</t>
+          <t>22476</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30860</t>
+          <t>30805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43807</t>
+          <t>43717</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>55704</t>
+          <t>55879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,33%</t>
+          <t>62,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,25%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4047</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2785</t>
+          <t>3951</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,32%</t>
         </is>
       </c>
     </row>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>4350</t>
+          <t>4118</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2457</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9542</t>
+          <t>9567</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5774</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>15555</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9721</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21323</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>31146</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38675</t>
+          <t>38711</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>38370</t>
+          <t>37787</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>47828</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>72272</t>
+          <t>71278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>84989</t>
+          <t>84679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>86,95%</t>
         </is>
       </c>
     </row>
@@ -2249,7 +2249,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4131</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2442</t>
+          <t>3378</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3042</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2338</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9984</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2541</t>
+          <t>2539</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>16719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,74%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>30828</t>
+          <t>30823</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38444</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>75,54%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27889</t>
+          <t>28512</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>35456</t>
+          <t>36027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,04%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61136</t>
+          <t>61563</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>72522</t>
+          <t>72329</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,71%</t>
         </is>
       </c>
     </row>
@@ -2818,7 +2818,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3575</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4137</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3009,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3315</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3431</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6387</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14509</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5940</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16474</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14157</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>27747</t>
+          <t>27604</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,61%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>26366</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35774</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>36017</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>46102</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66370</t>
+          <t>66389</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>79933</t>
+          <t>79695</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,58%</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4065</t>
+          <t>3690</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>2636</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2843</t>
+          <t>3506</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4674</t>
+          <t>5003</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>14538</t>
+          <t>15046</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3947,7 +3947,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>20916</t>
+          <t>20253</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -3962,7 +3962,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>37536</t>
+          <t>37756</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4217,7 +4217,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5318</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4275,7 +4275,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>5307</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>2701</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4388,7 +4388,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>4353</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>8055</t>
+          <t>8082</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4516,12 +4516,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2924</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5738</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>14816</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -4594,12 +4594,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>20834</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>28100</t>
+          <t>28111</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4629,12 +4629,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>22195</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>29323</t>
+          <t>29380</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4644,12 +4644,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>45850</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>55940</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4679,12 +4679,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>86,22%</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>3809</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>3902</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>642</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>5429</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>683</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1329</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1363</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2113</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9666</t>
+          <t>9168</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7493</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>17459</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>11106</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>12477</t>
+          <t>12458</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>25264</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,71%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>45674</t>
+          <t>46249</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>57885</t>
+          <t>58183</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>41606</t>
+          <t>41436</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>51909</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>91956</t>
+          <t>91294</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>106674</t>
+          <t>106366</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,04%</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3913</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>4812</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>689</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>6029</t>
+          <t>5995</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7653</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5634,12 +5634,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5654,12 +5654,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>605</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5689,12 +5689,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2199</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5704,12 +5704,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -5732,12 +5732,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>447</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5767,12 +5767,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>6737</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5802,12 +5802,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2121</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>9775</t>
+          <t>9809</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -5845,12 +5845,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>6156</t>
+          <t>6289</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16138</t>
+          <t>15892</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5860,12 +5860,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5503</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>15047</t>
+          <t>15017</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5915,12 +5915,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>13312</t>
+          <t>13982</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>26844</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5958,12 +5958,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>64252</t>
+          <t>64324</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>76340</t>
+          <t>76472</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5973,12 +5973,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5993,12 +5993,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>67975</t>
+          <t>67476</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>79606</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6028,12 +6028,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>136084</t>
+          <t>135908</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>152982</t>
+          <t>152496</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>76,7%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,06%</t>
         </is>
       </c>
     </row>
@@ -6188,12 +6188,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>763</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>6800</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6223,12 +6223,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1349</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6238,12 +6238,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6258,12 +6258,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>12021</t>
+          <t>11536</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6273,12 +6273,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -6301,12 +6301,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3556</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>12907</t>
+          <t>12909</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6336,12 +6336,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3427</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>11211</t>
+          <t>12715</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>8880</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>21260</t>
+          <t>21663</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -6414,12 +6414,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>14090</t>
+          <t>13791</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6429,12 +6429,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6449,12 +6449,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>25943</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -6527,12 +6527,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47013</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>71620</t>
+          <t>70260</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6562,12 +6562,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>45515</t>
+          <t>44917</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66526</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6597,12 +6597,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>96963</t>
+          <t>97791</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>128237</t>
+          <t>129354</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>278715</t>
+          <t>278170</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>303646</t>
+          <t>304111</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6675,12 +6675,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>303552</t>
+          <t>302472</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>326633</t>
+          <t>327219</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6710,12 +6710,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>589580</t>
+          <t>588313</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>624468</t>
+          <t>623294</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -7111,7 +7111,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3086</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7126,7 +7126,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7181,7 +7181,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4242</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7196,7 +7196,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -7259,7 +7259,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7274,7 +7274,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3296</t>
+          <t>3078</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -7337,7 +7337,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4893</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>505</t>
+          <t>494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5851</t>
+          <t>5230</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1160</t>
+          <t>1174</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3777</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>11141</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>15695</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>22210</t>
+          <t>22172</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18807</t>
+          <t>19153</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26081</t>
+          <t>25780</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,27%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37240</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46388</t>
+          <t>46353</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -7793,7 +7793,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7828,7 +7828,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3094</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7843,7 +7843,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>624</t>
+          <t>630</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5991</t>
+          <t>6088</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>626</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5172</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>8674</t>
+          <t>8719</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10367</t>
+          <t>11037</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9025</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6456</t>
+          <t>6486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17046</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35477</t>
+          <t>35476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>44775</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8260,7 +8260,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26410</t>
+          <t>26467</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>34642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64940</t>
+          <t>65243</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>77373</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,8%</t>
         </is>
       </c>
     </row>
@@ -8475,7 +8475,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>3347</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8505,12 +8505,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8540,12 +8540,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -8623,7 +8623,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8701,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3165</t>
+          <t>3838</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8716,7 +8716,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>710</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5963</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6257</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9135</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,2%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16175</t>
+          <t>16339</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22128</t>
+          <t>22109</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15424</t>
+          <t>15088</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>22697</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,7%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43621</t>
+          <t>43605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,61%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -9270,7 +9270,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3797</t>
+          <t>3329</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9285,7 +9285,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>3384</t>
+          <t>3388</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9355,7 +9355,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9378,12 +9378,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>452</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5389</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9393,12 +9393,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9418,7 +9418,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4205</t>
+          <t>4034</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9433,7 +9433,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9448,12 +9448,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>7187</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -9491,12 +9491,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2628</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>9415</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9526,12 +9526,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2432</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11114</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9561,12 +9561,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9576,12 +9576,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -9604,12 +9604,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22933</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>26032</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>34846</t>
+          <t>35232</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9654,12 +9654,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52610</t>
+          <t>52183</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>64452</t>
+          <t>63970</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9689,12 +9689,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>3618</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9924,7 +9924,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,21%</t>
         </is>
       </c>
     </row>
@@ -9987,7 +9987,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>4094</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10002,7 +10002,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10022,7 +10022,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3941</t>
+          <t>4093</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>758</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10188,12 +10188,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10243,12 +10243,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>731</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6066</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>17,61%</t>
         </is>
       </c>
     </row>
@@ -10286,12 +10286,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t>8040</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10301,12 +10301,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>14891</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -10356,12 +10356,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>24894</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32239</t>
+          <t>32293</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>72,28%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,77%</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>3790</t>
+          <t>3828</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10669,7 +10669,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10684,7 +10684,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4237</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10719,7 +10719,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -10855,12 +10855,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>5677</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10870,12 +10870,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10890,12 +10890,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>742</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10905,12 +10905,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10925,12 +10925,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2164</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10940,12 +10940,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -10968,12 +10968,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13822</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>19570</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10983,12 +10983,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>68,12%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11003,12 +11003,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>15928</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>21891</t>
+          <t>21909</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,02%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11038,12 +11038,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>32693</t>
+          <t>32389</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>40403</t>
+          <t>40432</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11053,12 +11053,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3102</t>
+          <t>3620</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11351,7 +11351,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>3002</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>4339</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11401,7 +11401,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>5106</t>
+          <t>4936</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11499,7 +11499,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -11537,12 +11537,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5960</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11552,12 +11552,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11572,12 +11572,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8735</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>19808</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11587,12 +11587,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11607,12 +11607,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>17016</t>
+          <t>16377</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>30366</t>
+          <t>31128</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11622,12 +11622,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -11650,12 +11650,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>42877</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>53082</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11665,12 +11665,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11685,12 +11685,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>44607</t>
+          <t>44841</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>55948</t>
+          <t>55842</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11700,12 +11700,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11720,12 +11720,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>91609</t>
+          <t>91545</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>106167</t>
+          <t>106836</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11735,12 +11735,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,54%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>4502</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11920,7 +11920,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11935,7 +11935,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>657</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>7045</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -12028,12 +12028,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>586</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5987</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12043,12 +12043,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>580</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>6451</t>
+          <t>5579</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -12106,12 +12106,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>1326</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>6344</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12176,12 +12176,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>2946</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>11064</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12191,12 +12191,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -12219,12 +12219,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>3933</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>12463</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4484</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12289,12 +12289,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>22339</t>
+          <t>22624</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12304,12 +12304,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -12332,12 +12332,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>69433</t>
+          <t>70350</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>80330</t>
+          <t>80656</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12347,12 +12347,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12367,12 +12367,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>74133</t>
+          <t>74156</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>85490</t>
+          <t>85399</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12402,12 +12402,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>147926</t>
+          <t>147300</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>163297</t>
+          <t>163237</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,34%</t>
         </is>
       </c>
     </row>
@@ -12562,12 +12562,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>8017</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12577,12 +12577,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2509</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>11050</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12612,12 +12612,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12632,12 +12632,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5395</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>16181</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12647,12 +12647,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -12675,12 +12675,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>644</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12710,12 +12710,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12725,12 +12725,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12745,12 +12745,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>12632</t>
+          <t>12442</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -12788,12 +12788,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>5810</t>
+          <t>6049</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>15876</t>
+          <t>15936</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12803,12 +12803,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12823,12 +12823,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>5313</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>15808</t>
+          <t>15242</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12838,12 +12838,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12858,12 +12858,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>28138</t>
+          <t>27609</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12873,12 +12873,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -12901,12 +12901,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>31600</t>
+          <t>31011</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>50564</t>
+          <t>50300</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12916,12 +12916,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12936,12 +12936,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>31409</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>50777</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12951,7 +12951,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -12971,12 +12971,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>67237</t>
+          <t>67471</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>94888</t>
+          <t>95253</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12986,12 +12986,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -13014,12 +13014,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>249229</t>
+          <t>248741</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>271182</t>
+          <t>271594</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13029,12 +13029,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>262098</t>
+          <t>262097</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>284226</t>
+          <t>285319</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13084,12 +13084,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>517267</t>
+          <t>518936</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>551568</t>
+          <t>551817</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13099,12 +13099,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,65%</t>
         </is>
       </c>
     </row>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3131</t>
+          <t>3529</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -13535,7 +13535,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -13570,7 +13570,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -13598,7 +13598,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3067</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -13613,7 +13613,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13633,7 +13633,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2639</t>
+          <t>2569</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -13648,7 +13648,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13663,12 +13663,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4347</t>
+          <t>4483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -13746,7 +13746,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -13761,7 +13761,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13781,7 +13781,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -13796,7 +13796,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -13819,12 +13819,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>9766</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -13834,12 +13834,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -13854,12 +13854,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1669</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7806</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -13869,12 +13869,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -13889,12 +13889,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>6438</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15261</t>
+          <t>14650</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -13904,12 +13904,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -13932,12 +13932,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14856</t>
+          <t>14959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21686</t>
+          <t>21756</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -13947,12 +13947,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,37%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>84,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -13967,12 +13967,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28920</t>
+          <t>28560</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -13982,12 +13982,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>68,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14002,12 +14002,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39564</t>
+          <t>39397</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>49160</t>
+          <t>48893</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -14017,12 +14017,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>84,8%</t>
         </is>
       </c>
     </row>
@@ -14167,7 +14167,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4399</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14237,7 +14237,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4440</t>
+          <t>4472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -14252,7 +14252,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,25%</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -14330,7 +14330,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -14365,7 +14365,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -14393,7 +14393,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -14428,7 +14428,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>4389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14443,7 +14443,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -14458,12 +14458,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>5899</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14478,7 +14478,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -14501,12 +14501,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>6950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -14516,12 +14516,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -14536,12 +14536,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6637</t>
+          <t>7174</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -14551,12 +14551,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14571,12 +14571,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3533</t>
+          <t>3634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11788</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -14586,12 +14586,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14614,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25340</t>
+          <t>25271</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32275</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -14629,12 +14629,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14649,12 +14649,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>34052</t>
+          <t>34086</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -14664,12 +14664,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14684,12 +14684,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>54916</t>
+          <t>55117</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65026</t>
+          <t>64808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -14699,12 +14699,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,64%</t>
         </is>
       </c>
     </row>
@@ -15075,7 +15075,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3549</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -15183,12 +15183,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>821</t>
+          <t>798</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -15198,12 +15198,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15218,12 +15218,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15233,12 +15233,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15253,12 +15253,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12941</t>
+          <t>13735</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -15268,12 +15268,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,62%</t>
         </is>
       </c>
     </row>
@@ -15296,12 +15296,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22851</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -15311,12 +15311,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15331,12 +15331,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>30356</t>
+          <t>30420</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>37298</t>
+          <t>37256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -15346,12 +15346,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15366,12 +15366,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56244</t>
+          <t>55796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65248</t>
+          <t>65109</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -15381,12 +15381,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>79,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>92,99%</t>
         </is>
       </c>
     </row>
@@ -15531,7 +15531,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -15546,7 +15546,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -15566,7 +15566,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -15581,7 +15581,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -15596,12 +15596,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6545</t>
+          <t>5907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -15616,7 +15616,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -15659,7 +15659,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -15679,7 +15679,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>4295</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15709,12 +15709,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>692</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>5761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -15724,12 +15724,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5051</t>
+          <t>5025</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -15792,7 +15792,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2850</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -15827,7 +15827,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5714</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -15842,7 +15842,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6288</t>
+          <t>5837</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -15880,12 +15880,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -15905,7 +15905,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -15920,7 +15920,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -15935,12 +15935,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1402</t>
+          <t>1381</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8322</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -15950,12 +15950,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -15978,12 +15978,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23004</t>
+          <t>22522</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30312</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -15993,12 +15993,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16013,12 +16013,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25802</t>
+          <t>25400</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -16028,12 +16028,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16048,12 +16048,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51086</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60833</t>
+          <t>60775</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -16063,12 +16063,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,82%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -16361,7 +16361,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2902</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -16376,7 +16376,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>3302</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,99%</t>
         </is>
       </c>
     </row>
@@ -16474,7 +16474,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>3207</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16489,7 +16489,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2675</t>
+          <t>2819</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16524,7 +16524,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,68%</t>
         </is>
       </c>
     </row>
@@ -16587,7 +16587,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -16602,7 +16602,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16622,7 +16622,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2810</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -16637,7 +16637,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -16695,12 +16695,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>16795</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21024</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -16710,12 +16710,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16730,12 +16730,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>32500</t>
+          <t>32376</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36204</t>
+          <t>36181</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -16745,12 +16745,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -16930,7 +16930,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -16945,7 +16945,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -16965,7 +16965,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3884</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -17008,7 +17008,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4570</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17043,7 +17043,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4745</t>
+          <t>4846</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -17058,7 +17058,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17073,12 +17073,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>613</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6082</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -17088,12 +17088,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -17121,7 +17121,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17156,7 +17156,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>4623</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17186,12 +17186,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>710</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -17201,12 +17201,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -17229,12 +17229,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1393</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -17244,12 +17244,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17264,12 +17264,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>729</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>6748</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -17279,12 +17279,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17299,12 +17299,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -17314,12 +17314,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -17342,12 +17342,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15832</t>
+          <t>16031</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>22974</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -17357,12 +17357,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17377,12 +17377,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>28848</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17412,12 +17412,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>40060</t>
+          <t>39718</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>50378</t>
+          <t>50354</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17427,12 +17427,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>68,51%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,86%</t>
         </is>
       </c>
     </row>
@@ -17607,12 +17607,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>702</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -17627,7 +17627,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -17642,12 +17642,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>704</t>
+          <t>705</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>5899</t>
+          <t>6532</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -17662,7 +17662,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -17803,7 +17803,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -17833,12 +17833,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>6976</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -17848,12 +17848,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>9629</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -17883,12 +17883,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -17911,12 +17911,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5655</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>15926</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -17926,12 +17926,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -17946,12 +17946,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>10748</t>
+          <t>11271</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -17981,12 +17981,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10360</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>22713</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -17996,12 +17996,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -18024,12 +18024,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>69632</t>
+          <t>70084</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>80277</t>
+          <t>80115</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -18039,12 +18039,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -18059,12 +18059,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>68605</t>
+          <t>68961</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>79087</t>
+          <t>79384</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -18074,12 +18074,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>79,22%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -18094,12 +18094,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>142445</t>
+          <t>142186</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>157290</t>
+          <t>157376</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -18109,12 +18109,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,73%</t>
         </is>
       </c>
     </row>
@@ -18294,7 +18294,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -18309,7 +18309,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -18329,7 +18329,7 @@
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2755</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>3330</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -18485,7 +18485,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4501</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -18500,7 +18500,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -18515,12 +18515,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1194</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -18530,12 +18530,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -18550,12 +18550,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1727</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8669</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -18565,12 +18565,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -18593,12 +18593,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5480</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>14775</t>
+          <t>15200</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -18608,12 +18608,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -18628,12 +18628,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>4328</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>13144</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -18643,12 +18643,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -18663,12 +18663,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -18678,12 +18678,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -18706,12 +18706,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>67355</t>
+          <t>67688</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>76983</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -18721,12 +18721,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -18741,12 +18741,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>72945</t>
+          <t>73329</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>83419</t>
+          <t>83451</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -18756,12 +18756,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -18776,12 +18776,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>143586</t>
+          <t>144051</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>158028</t>
+          <t>158333</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -18791,12 +18791,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>82,09%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,52%</t>
         </is>
       </c>
     </row>
@@ -18936,12 +18936,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>725</t>
+          <t>723</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>6825</t>
+          <t>7013</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -18951,12 +18951,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -18971,12 +18971,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10617</t>
+          <t>9600</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -18986,12 +18986,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>12669</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -19021,12 +19021,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -19049,12 +19049,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1447</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>7795</t>
+          <t>7570</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1660</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>8892</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -19099,12 +19099,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -19119,12 +19119,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4106</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>13113</t>
+          <t>12800</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -19134,12 +19134,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -19162,12 +19162,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>3057</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>11335</t>
+          <t>12150</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -19177,12 +19177,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -19197,12 +19197,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -19212,12 +19212,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -19232,12 +19232,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>11911</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>25156</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -19247,12 +19247,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -19275,12 +19275,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>29478</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>46760</t>
+          <t>46838</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -19290,12 +19290,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -19310,12 +19310,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>24023</t>
+          <t>23535</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40474</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -19325,12 +19325,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -19345,12 +19345,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>57332</t>
+          <t>58119</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84493</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -19360,12 +19360,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -19388,12 +19388,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>276656</t>
+          <t>274531</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>295781</t>
+          <t>295688</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -19403,12 +19403,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -19423,12 +19423,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>309397</t>
+          <t>308410</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>329914</t>
+          <t>331188</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -19438,12 +19438,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,99%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -19458,12 +19458,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>590035</t>
+          <t>588387</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>620637</t>
+          <t>620559</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -19473,12 +19473,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
